--- a/Model objective analysis/Capacity increase/sensitivity_and_comparison/base model/OBJ Calculation Check.xlsx
+++ b/Model objective analysis/Capacity increase/sensitivity_and_comparison/base model/OBJ Calculation Check.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Model objective analysis/Capacity increase/sensitivity_and_comparison/base model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1963BF53-1A02-45C9-93DD-0AFDB44E49B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{1963BF53-1A02-45C9-93DD-0AFDB44E49B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F495405-66CA-42E4-BA86-1916D73DB7F5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3B3BC660-8798-403C-B571-588C0DB056E7}"/>
   </bookViews>
@@ -151,7 +151,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -273,7 +273,7 @@
     <xf numFmtId="11" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
